--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_zarrukNeurologicalTestsFunctional2011.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_zarrukNeurologicalTestsFunctional2011.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809CF78D-67C8-D446-9C48-17BECA0DC670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20245645-982D-BA44-ACCB-9F2400094963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38360" yWindow="4000" windowWidth="27640" windowHeight="16940" xr2:uid="{31FB5D06-B587-8446-8044-53A870570460}"/>
+    <workbookView xWindow="43800" yWindow="8020" windowWidth="27640" windowHeight="16940" xr2:uid="{31FB5D06-B587-8446-8044-53A870570460}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Test Name</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Subdomain</t>
   </si>
   <si>
-    <t>Sensorimotor</t>
-  </si>
-  <si>
     <t>Morris water maze</t>
   </si>
   <si>
@@ -182,7 +179,7 @@
     <t>Global neurological function</t>
   </si>
   <si>
-    <t>Cognitive</t>
+    <t>Behavioral</t>
   </si>
 </sst>
 </file>
@@ -593,7 +590,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -607,7 +604,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -621,7 +618,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -635,7 +632,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -649,7 +646,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -663,7 +660,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -677,7 +674,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -691,7 +688,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -705,7 +702,7 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -719,7 +716,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
@@ -733,7 +730,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -741,58 +738,58 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
